--- a/events/Pau_2020_WC/Pau_2020_WC_start.xlsx
+++ b/events/Pau_2020_WC/Pau_2020_WC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W358"/>
+  <dimension ref="A1:AC356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -1857,7 +1887,7 @@
           <t>ROSSI Carolina</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>55806</t>
         </is>
@@ -1915,7 +1945,7 @@
           <t>BALDONI Lea</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>94529</t>
         </is>
@@ -1973,7 +2003,7 @@
           <t>ARREGUI Olatz</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>69083</t>
         </is>
@@ -2031,7 +2061,7 @@
           <t>CORCORAN Madison</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>106163</t>
         </is>
@@ -2089,7 +2119,7 @@
           <t>FONT VOORHOEVE Noemi</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>83555</t>
         </is>
@@ -2147,7 +2177,7 @@
           <t>CRAIG Hannah</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>35815</t>
         </is>
@@ -2205,7 +2235,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -2263,7 +2293,7 @@
           <t>KUZNETSOVA Daria</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>76780</t>
         </is>
@@ -2321,7 +2351,7 @@
           <t>REINOSO Sofia</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>45745</t>
         </is>
@@ -2379,7 +2409,7 @@
           <t>RAZEGHIAN Roxana</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>63124</t>
         </is>
@@ -2437,7 +2467,7 @@
           <t>OTTEN Maartje</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>35337</t>
         </is>
@@ -2495,7 +2525,7 @@
           <t>COLLIN Georgina</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>60108</t>
         </is>
@@ -2553,7 +2583,7 @@
           <t>KRYLOVA Kseniia</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>60639</t>
         </is>
@@ -2611,7 +2641,7 @@
           <t>BEKOVA Katerina</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>77167</t>
         </is>
@@ -2669,7 +2699,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -2727,7 +2757,7 @@
           <t>SRIBAR Ria</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>75645</t>
         </is>
@@ -2785,7 +2815,7 @@
           <t>NESNIDALOVA Lucie</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>75449</t>
         </is>
@@ -2843,7 +2873,7 @@
           <t>PRIGENT Romane</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>71968</t>
         </is>
@@ -2901,7 +2931,7 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>53314</t>
         </is>
@@ -2959,7 +2989,7 @@
           <t>SORRIBES Laia</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>68822</t>
         </is>
@@ -3017,7 +3047,7 @@
           <t>DORIA VILARRUBLA Monica</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -3075,7 +3105,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -3133,7 +3163,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -3191,7 +3221,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -3249,7 +3279,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -3307,7 +3337,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -3365,7 +3395,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -3423,7 +3453,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -3481,7 +3511,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -3539,7 +3569,7 @@
           <t>UKALOVIC Thomas</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>93708</t>
         </is>
@@ -3597,7 +3627,7 @@
           <t>AIT KADDOUR Nour</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>96649</t>
         </is>
@@ -3655,7 +3685,7 @@
           <t>FRIEDENSON Kaelin</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>87397</t>
         </is>
@@ -3713,7 +3743,7 @@
           <t>MORLEY Tom</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>84239</t>
         </is>
@@ -3771,7 +3801,7 @@
           <t>CUESTA Dario</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>84242</t>
         </is>
@@ -3829,7 +3859,7 @@
           <t>KORPES Ren</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>39941</t>
         </is>
@@ -3887,7 +3917,7 @@
           <t>JOSEPH Joshua</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>69141</t>
         </is>
@@ -3945,7 +3975,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -4003,7 +4033,7 @@
           <t>SOUDI Mathis</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>69447</t>
         </is>
@@ -4061,7 +4091,7 @@
           <t>ZIMA Tomas</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>60019</t>
         </is>
@@ -4119,7 +4149,7 @@
           <t>DESNOS Mathieu</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>93791</t>
         </is>
@@ -4177,7 +4207,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -4235,7 +4265,7 @@
           <t>DELASSUS Anatole</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>84109</t>
         </is>
@@ -4293,7 +4323,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -4351,7 +4381,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -4409,7 +4439,7 @@
           <t>RENIA Benjamin</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>35407</t>
         </is>
@@ -4467,7 +4497,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -4525,7 +4555,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -4583,7 +4613,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -4641,7 +4671,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -4699,7 +4729,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -4757,7 +4787,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -4815,7 +4845,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -4873,7 +4903,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -4931,7 +4961,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -4989,7 +5019,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -5047,7 +5077,7 @@
           <t>KUZNETSOVA Daria</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>76780</t>
         </is>
@@ -5105,7 +5135,7 @@
           <t>KNEBLOVA Klara</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>104899</t>
         </is>
@@ -5163,7 +5193,7 @@
           <t>FONT VOORHOEVE Noemi</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>83555</t>
         </is>
@@ -5221,7 +5251,7 @@
           <t>TORRES BRICENO Marianna</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>75357</t>
         </is>
@@ -5279,7 +5309,7 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -5337,7 +5367,7 @@
           <t>CORCORAN Michaela</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>106164</t>
         </is>
@@ -5395,7 +5425,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -5453,7 +5483,7 @@
           <t>KOZYREVA Anastasia</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>60640</t>
         </is>
@@ -5511,7 +5541,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -5569,7 +5599,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -5627,7 +5657,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -5685,7 +5715,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -5743,7 +5773,7 @@
           <t>RIHOVA Eva</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>51791</t>
         </is>
@@ -5801,7 +5831,7 @@
           <t>DELASSUS Marjorie</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>71964</t>
         </is>
@@ -5859,7 +5889,7 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>53314</t>
         </is>
@@ -5917,7 +5947,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -5975,7 +6005,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -6033,7 +6063,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -6091,7 +6121,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -6149,7 +6179,7 @@
           <t>DORIA VILARRUBLA Monica</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -6207,7 +6237,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -6265,7 +6295,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -6323,7 +6353,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -6381,7 +6411,7 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -6439,7 +6469,7 @@
           <t>KLEVLEEV Anvar</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>130188</t>
         </is>
@@ -6497,7 +6527,7 @@
           <t>PEREZ Daniel</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>84367</t>
         </is>
@@ -6555,7 +6585,7 @@
           <t>SARAMANDIF Terence</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>79340</t>
         </is>
@@ -6613,7 +6643,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -6671,7 +6701,7 @@
           <t>BOURHIS Yves</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>63237</t>
         </is>
@@ -6729,7 +6759,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -6787,7 +6817,7 @@
           <t>FERNANDEZ Luis</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -6845,7 +6875,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -6903,7 +6933,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -6961,7 +6991,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -7019,7 +7049,7 @@
           <t>BERNARDET Jules</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>84123</t>
         </is>
@@ -7077,7 +7107,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -7135,7 +7165,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -7193,7 +7223,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -7251,7 +7281,7 @@
           <t>CHALOUPKA Vaclav</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>51648</t>
         </is>
@@ -7309,7 +7339,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -7367,7 +7397,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -7425,7 +7455,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -7483,7 +7513,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -7541,7 +7571,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -7811,7 +7841,7 @@
           <t>ROSSI Carolina</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>55806</t>
         </is>
@@ -7869,7 +7899,7 @@
           <t>BALDONI Lea</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>94529</t>
         </is>
@@ -7927,7 +7957,7 @@
           <t>ARREGUI Olatz</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>69083</t>
         </is>
@@ -7985,7 +8015,7 @@
           <t>CORCORAN Madison</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>106163</t>
         </is>
@@ -8043,7 +8073,7 @@
           <t>FONT VOORHOEVE Noemi</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>83555</t>
         </is>
@@ -8101,7 +8131,7 @@
           <t>CRAIG Hannah</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>35815</t>
         </is>
@@ -8159,7 +8189,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -8217,7 +8247,7 @@
           <t>KUZNETSOVA Daria</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>76780</t>
         </is>
@@ -8275,7 +8305,7 @@
           <t>REINOSO Sofia</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>45745</t>
         </is>
@@ -8333,7 +8363,7 @@
           <t>RAZEGHIAN Roxana</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>63124</t>
         </is>
@@ -8391,7 +8421,7 @@
           <t>OTTEN Maartje</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>35337</t>
         </is>
@@ -8449,7 +8479,7 @@
           <t>COLLIN Georgina</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>60108</t>
         </is>
@@ -8507,7 +8537,7 @@
           <t>KRYLOVA Kseniia</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>60639</t>
         </is>
@@ -8565,7 +8595,7 @@
           <t>BEKOVA Katerina</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>77167</t>
         </is>
@@ -8623,7 +8653,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -8681,7 +8711,7 @@
           <t>SRIBAR Ria</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>75645</t>
         </is>
@@ -8739,7 +8769,7 @@
           <t>NESNIDALOVA Lucie</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>75449</t>
         </is>
@@ -8797,7 +8827,7 @@
           <t>PRIGENT Romane</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>71968</t>
         </is>
@@ -8855,7 +8885,7 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>53314</t>
         </is>
@@ -8913,7 +8943,7 @@
           <t>SORRIBES Laia</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>68822</t>
         </is>
@@ -8971,7 +9001,7 @@
           <t>DORIA VILARRUBLA Monica</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -9029,7 +9059,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -9087,7 +9117,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -9145,7 +9175,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -9203,7 +9233,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -9261,7 +9291,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -9319,7 +9349,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -9377,7 +9407,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -9435,7 +9465,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -9493,7 +9523,7 @@
           <t>UKALOVIC Thomas</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>93708</t>
         </is>
@@ -9551,7 +9581,7 @@
           <t>AIT KADDOUR Nour</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>96649</t>
         </is>
@@ -9609,7 +9639,7 @@
           <t>FRIEDENSON Kaelin</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>87397</t>
         </is>
@@ -9667,7 +9697,7 @@
           <t>MORLEY Tom</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>84239</t>
         </is>
@@ -9725,7 +9755,7 @@
           <t>CUESTA Dario</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>84242</t>
         </is>
@@ -9783,7 +9813,7 @@
           <t>KORPES Ren</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="X163" t="inlineStr">
         <is>
           <t>39941</t>
         </is>
@@ -9841,7 +9871,7 @@
           <t>JOSEPH Joshua</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>69141</t>
         </is>
@@ -9899,7 +9929,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -9957,7 +9987,7 @@
           <t>SOUDI Mathis</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>69447</t>
         </is>
@@ -10015,7 +10045,7 @@
           <t>ZIMA Tomas</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>60019</t>
         </is>
@@ -10073,7 +10103,7 @@
           <t>DESNOS Mathieu</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>93791</t>
         </is>
@@ -10131,7 +10161,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -10189,7 +10219,7 @@
           <t>DELASSUS Anatole</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>84109</t>
         </is>
@@ -10247,7 +10277,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -10305,7 +10335,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -10363,7 +10393,7 @@
           <t>RENIA Benjamin</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>35407</t>
         </is>
@@ -10421,7 +10451,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -10479,7 +10509,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -10537,7 +10567,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -10595,7 +10625,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -10653,7 +10683,7 @@
           <t>LAUNAY Antoine</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>68776</t>
         </is>
@@ -10711,7 +10741,7 @@
           <t>CRESPO Joan</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>35749</t>
         </is>
@@ -10769,7 +10799,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -10827,7 +10857,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -10885,7 +10915,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -10943,7 +10973,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -11011,7 +11041,7 @@
           <t>OTTEN Maartje</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>35337</t>
         </is>
@@ -11079,7 +11109,7 @@
           <t>ARREGUI Olatz</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>69083</t>
         </is>
@@ -11147,7 +11177,7 @@
           <t>BEKOVA Katerina</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>77167</t>
         </is>
@@ -11215,7 +11245,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -11283,7 +11313,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -11351,7 +11381,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -11419,7 +11449,7 @@
           <t>CHOURRAUT Maialen</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>35787</t>
         </is>
@@ -11487,7 +11517,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -11555,7 +11585,7 @@
           <t>LAFONT Marie-Zelia</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>35374</t>
         </is>
@@ -11623,7 +11653,7 @@
           <t>PRIGENT Romane</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>71968</t>
         </is>
@@ -11691,7 +11721,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -11759,7 +11789,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -11827,7 +11857,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -11895,7 +11925,7 @@
           <t>JOSEPH Joshua</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>69141</t>
         </is>
@@ -11963,7 +11993,7 @@
           <t>DESNOS Mathieu</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>93791</t>
         </is>
@@ -12031,7 +12061,7 @@
           <t>DOUGOUD Martin</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>35426</t>
         </is>
@@ -12099,7 +12129,7 @@
           <t>RENIA Benjamin</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>35407</t>
         </is>
@@ -12167,7 +12197,7 @@
           <t>ZIMA Tomas</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
+      <c r="X201" t="inlineStr">
         <is>
           <t>60019</t>
         </is>
@@ -12235,7 +12265,7 @@
           <t>DELASSUS Anatole</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>84109</t>
         </is>
@@ -12303,7 +12333,7 @@
           <t>PRINDIS Vit</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>35065</t>
         </is>
@@ -12366,7 +12396,7 @@
           <t>TORRES BRICENO Marianna</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>75357</t>
         </is>
@@ -12429,7 +12459,7 @@
           <t>DELASSUS Natacha</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>84184</t>
         </is>
@@ -12492,7 +12522,7 @@
           <t>ARREGUI Olatz</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>69083</t>
         </is>
@@ -12555,7 +12585,7 @@
           <t>SABITOVA Zulfiia</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -12618,7 +12648,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -12681,7 +12711,7 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>53314</t>
         </is>
@@ -12744,7 +12774,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -12807,7 +12837,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -12870,7 +12900,7 @@
           <t>KUZNETSOVA Daria</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>76780</t>
         </is>
@@ -12933,7 +12963,7 @@
           <t>DEGREMONT Alix</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>71794</t>
         </is>
@@ -12996,7 +13026,7 @@
           <t>PRIGENT Romane</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>71968</t>
         </is>
@@ -13059,7 +13089,7 @@
           <t>BALDONI Lea</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>94529</t>
         </is>
@@ -13122,7 +13152,7 @@
           <t>REINOSO Sofia</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
+      <c r="X216" t="inlineStr">
         <is>
           <t>45745</t>
         </is>
@@ -13185,7 +13215,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -13248,7 +13278,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -13311,7 +13341,7 @@
           <t>MORLEY Tom</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>84239</t>
         </is>
@@ -13374,7 +13404,7 @@
           <t>ZIMA Tomas</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="X220" t="inlineStr">
         <is>
           <t>60019</t>
         </is>
@@ -13437,7 +13467,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -13500,7 +13530,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -13563,7 +13593,7 @@
           <t>AIT KADDOUR Nour</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>96649</t>
         </is>
@@ -13626,7 +13656,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -13689,7 +13719,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -13752,7 +13782,7 @@
           <t>RENIA Benjamin</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>35407</t>
         </is>
@@ -13815,7 +13845,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -13878,7 +13908,7 @@
           <t>FRIEDENSON Kaelin</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>87397</t>
         </is>
@@ -13941,7 +13971,7 @@
           <t>FISCHER Adrien</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>84089</t>
         </is>
@@ -14004,7 +14034,7 @@
           <t>UKALOVIC Thomas</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>93708</t>
         </is>
@@ -14067,7 +14097,7 @@
           <t>CUESTA Dario</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>84242</t>
         </is>
@@ -14130,7 +14160,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="X232" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -14193,7 +14223,7 @@
           <t>MARTEIL Valentin</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>71962</t>
         </is>
@@ -14256,7 +14286,7 @@
           <t>SARAMANDIF Terence</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>79340</t>
         </is>
@@ -14319,7 +14349,7 @@
           <t>ARREGUI Olatz</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>69083</t>
         </is>
@@ -14382,7 +14412,7 @@
           <t>DEGREMONT Alix</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr">
+      <c r="X236" t="inlineStr">
         <is>
           <t>71794</t>
         </is>
@@ -14445,7 +14475,7 @@
           <t>REINOSO Sofia</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
+      <c r="X237" t="inlineStr">
         <is>
           <t>45745</t>
         </is>
@@ -14508,7 +14538,7 @@
           <t>DELASSUS Natacha</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>84184</t>
         </is>
@@ -14571,7 +14601,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -14634,7 +14664,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -14697,7 +14727,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -14760,7 +14790,7 @@
           <t>BALDONI Lea</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>94529</t>
         </is>
@@ -14823,7 +14853,7 @@
           <t>KUZNETSOVA Daria</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>76780</t>
         </is>
@@ -14886,7 +14916,7 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>53314</t>
         </is>
@@ -14949,7 +14979,7 @@
           <t>TORRES BRICENO Marianna</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>75357</t>
         </is>
@@ -15012,7 +15042,7 @@
           <t>PRIGENT Romane</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>71968</t>
         </is>
@@ -15075,7 +15105,7 @@
           <t>SABITOVA Zulfiia</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -15138,7 +15168,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
+      <c r="X248" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -15201,7 +15231,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -15264,7 +15294,7 @@
           <t>RENIA Benjamin</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>35407</t>
         </is>
@@ -15327,7 +15357,7 @@
           <t>SARAMANDIF Terence</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>79340</t>
         </is>
@@ -15390,7 +15420,7 @@
           <t>UKALOVIC Thomas</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>93708</t>
         </is>
@@ -15453,7 +15483,7 @@
           <t>FISCHER Adrien</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>84089</t>
         </is>
@@ -15516,7 +15546,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -15579,7 +15609,7 @@
           <t>MORLEY Tom</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>84239</t>
         </is>
@@ -15642,7 +15672,7 @@
           <t>ZIMA Tomas</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
+      <c r="X256" t="inlineStr">
         <is>
           <t>60019</t>
         </is>
@@ -15705,7 +15735,7 @@
           <t>AIT KADDOUR Nour</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>96649</t>
         </is>
@@ -15768,7 +15798,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -15831,7 +15861,7 @@
           <t>CUESTA Dario</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>84242</t>
         </is>
@@ -15894,7 +15924,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -15957,7 +15987,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -16020,7 +16050,7 @@
           <t>FRIEDENSON Kaelin</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>87397</t>
         </is>
@@ -16083,7 +16113,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -16146,7 +16176,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -16209,7 +16239,7 @@
           <t>DEGREMONT Alix</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>71794</t>
         </is>
@@ -16272,7 +16302,7 @@
           <t>DELASSUS Natacha</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>84184</t>
         </is>
@@ -16335,7 +16365,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -16398,7 +16428,7 @@
           <t>REINOSO Sofia</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>45745</t>
         </is>
@@ -16461,7 +16491,7 @@
           <t>BALDONI Lea</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>94529</t>
         </is>
@@ -16524,7 +16554,7 @@
           <t>KUZNETSOVA Daria</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>76780</t>
         </is>
@@ -16587,7 +16617,7 @@
           <t>PRIGENT Romane</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>71968</t>
         </is>
@@ -16650,7 +16680,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -16713,7 +16743,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -16776,7 +16806,7 @@
           <t>RENIA Benjamin</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>35407</t>
         </is>
@@ -16839,7 +16869,7 @@
           <t>UKALOVIC Thomas</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>93708</t>
         </is>
@@ -16902,7 +16932,7 @@
           <t>ZIMA Tomas</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>60019</t>
         </is>
@@ -16965,7 +16995,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
+      <c r="X277" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -17028,7 +17058,7 @@
           <t>CUESTA Dario</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>84242</t>
         </is>
@@ -17091,7 +17121,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -17154,7 +17184,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -17227,7 +17257,7 @@
           <t>BALDONI Lea</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
+      <c r="X281" t="inlineStr">
         <is>
           <t>94529</t>
         </is>
@@ -17290,7 +17320,7 @@
           <t>DELASSUS Natacha</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>84184</t>
         </is>
@@ -17363,7 +17393,7 @@
           <t>REINOSO Sofia</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>45745</t>
         </is>
@@ -17436,7 +17466,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -17499,7 +17529,7 @@
           <t>CUESTA Dario</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>84242</t>
         </is>
@@ -17572,7 +17602,7 @@
           <t>EIGEL Pavel</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>35458</t>
         </is>
@@ -17635,7 +17665,7 @@
           <t>GONCALVES Pedro</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>38017</t>
         </is>
@@ -17698,7 +17728,7 @@
           <t>RENIA Benjamin</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>35407</t>
         </is>
@@ -17968,7 +17998,7 @@
           <t>KUZNETSOVA Daria</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>76780</t>
         </is>
@@ -18026,7 +18056,7 @@
           <t>KNEBLOVA Klara</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>104899</t>
         </is>
@@ -18084,7 +18114,7 @@
           <t>FONT VOORHOEVE Noemi</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>83555</t>
         </is>
@@ -18142,7 +18172,7 @@
           <t>TORRES BRICENO Marianna</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>75357</t>
         </is>
@@ -18200,7 +18230,7 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -18258,7 +18288,7 @@
           <t>CORCORAN Michaela</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>106164</t>
         </is>
@@ -18316,7 +18346,7 @@
           <t>PELLICER CHICA Laura</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>43129</t>
         </is>
@@ -18374,7 +18404,7 @@
           <t>KOZYREVA Anastasia</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>60640</t>
         </is>
@@ -18432,7 +18462,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -18490,7 +18520,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -18548,7 +18578,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -18606,7 +18636,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -18664,7 +18694,7 @@
           <t>RIHOVA Eva</t>
         </is>
       </c>
-      <c r="U305" t="inlineStr">
+      <c r="X305" t="inlineStr">
         <is>
           <t>51791</t>
         </is>
@@ -18722,7 +18752,7 @@
           <t>DELASSUS Marjorie</t>
         </is>
       </c>
-      <c r="U306" t="inlineStr">
+      <c r="X306" t="inlineStr">
         <is>
           <t>71964</t>
         </is>
@@ -18780,7 +18810,7 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U307" t="inlineStr">
+      <c r="X307" t="inlineStr">
         <is>
           <t>53314</t>
         </is>
@@ -18838,7 +18868,7 @@
           <t>LEIBFARTH Evy</t>
         </is>
       </c>
-      <c r="U308" t="inlineStr">
+      <c r="X308" t="inlineStr">
         <is>
           <t>83538</t>
         </is>
@@ -18896,7 +18926,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U309" t="inlineStr">
+      <c r="X309" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -18954,7 +18984,7 @@
           <t>FOX Noemie</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr">
+      <c r="X310" t="inlineStr">
         <is>
           <t>44812</t>
         </is>
@@ -19012,7 +19042,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
+      <c r="X311" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -19070,7 +19100,7 @@
           <t>DORIA VILARRUBLA Monica</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>53051</t>
         </is>
@@ -19128,7 +19158,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -19186,7 +19216,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
+      <c r="X314" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -19244,7 +19274,7 @@
           <t>BALDONI Alex</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>94528</t>
         </is>
@@ -19302,7 +19332,7 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
+      <c r="X316" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -19360,7 +19390,7 @@
           <t>KLEVLEEV Anvar</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>130188</t>
         </is>
@@ -19418,7 +19448,7 @@
           <t>PEREZ Daniel</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>84367</t>
         </is>
@@ -19476,7 +19506,7 @@
           <t>SARAMANDIF Terence</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>79340</t>
         </is>
@@ -19534,7 +19564,7 @@
           <t>OTTEN Joris</t>
         </is>
       </c>
-      <c r="U320" t="inlineStr">
+      <c r="X320" t="inlineStr">
         <is>
           <t>41698</t>
         </is>
@@ -19592,7 +19622,7 @@
           <t>BOURHIS Yves</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr">
+      <c r="X321" t="inlineStr">
         <is>
           <t>63237</t>
         </is>
@@ -19650,7 +19680,7 @@
           <t>BORGES Felipe</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="X322" t="inlineStr">
         <is>
           <t>38012</t>
         </is>
@@ -19708,7 +19738,7 @@
           <t>FERNANDEZ Luis</t>
         </is>
       </c>
-      <c r="U323" t="inlineStr">
+      <c r="X323" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -19766,7 +19796,7 @@
           <t>BOURHIS Jean Pierre</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>36968</t>
         </is>
@@ -19824,7 +19854,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -19882,7 +19912,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -19940,7 +19970,7 @@
           <t>BERNARDET Jules</t>
         </is>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>84123</t>
         </is>
@@ -19998,7 +20028,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -20056,7 +20086,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -20114,7 +20144,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U330" t="inlineStr">
+      <c r="X330" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -20172,7 +20202,7 @@
           <t>CHALOUPKA Vaclav</t>
         </is>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>51648</t>
         </is>
@@ -20230,7 +20260,7 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>35419</t>
         </is>
@@ -20288,7 +20318,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U333" t="inlineStr">
+      <c r="X333" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -20346,7 +20376,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -20404,7 +20434,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -20462,7 +20492,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -20530,7 +20560,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="X337" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -20598,7 +20628,7 @@
           <t>SATILA Ana</t>
         </is>
       </c>
-      <c r="U338" t="inlineStr">
+      <c r="X338" t="inlineStr">
         <is>
           <t>35327</t>
         </is>
@@ -20666,7 +20696,7 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -20734,7 +20764,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -20802,7 +20832,7 @@
           <t>LAZKANO Miren</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>35748</t>
         </is>
@@ -20870,7 +20900,7 @@
           <t>MINAZOVA Alsu</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>53314</t>
         </is>
@@ -20938,7 +20968,7 @@
           <t>RIHOVA Eva</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr">
+      <c r="X343" t="inlineStr">
         <is>
           <t>51791</t>
         </is>
@@ -21006,7 +21036,7 @@
           <t>HUG Angele</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>78746</t>
         </is>
@@ -21074,7 +21104,7 @@
           <t>VILARRUBLA Nuria</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>35746</t>
         </is>
@@ -21142,7 +21172,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr">
+      <c r="X346" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -21210,7 +21240,7 @@
           <t>FERNANDEZ Luis</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>51851</t>
         </is>
@@ -21278,7 +21308,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -21346,7 +21376,7 @@
           <t>ROHAN Lukas</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>36114</t>
         </is>
@@ -21414,7 +21444,7 @@
           <t>BOURHIS Yves</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
+      <c r="X350" t="inlineStr">
         <is>
           <t>63237</t>
         </is>
@@ -21482,7 +21512,7 @@
           <t>JEGOU Liam</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>35820</t>
         </is>
@@ -21550,7 +21580,7 @@
           <t>CHALOUPKA Vaclav</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>51648</t>
         </is>
@@ -21618,7 +21648,7 @@
           <t>HEGER Vojtech</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>68872</t>
         </is>
@@ -21686,7 +21716,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U354" t="inlineStr">
+      <c r="X354" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -21754,7 +21784,7 @@
           <t>TRAVE Miquel</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>68998</t>
         </is>
@@ -21822,135 +21852,9 @@
           <t>KOECHLIN Thomas</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
+      <c r="X356" t="inlineStr">
         <is>
           <t>35419</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="B357" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="E357" t="inlineStr">
-        <is>
-          <t>Time Trials</t>
-        </is>
-      </c>
-      <c r="F357" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G357" t="inlineStr">
-        <is>
-          <t>2020-11-08</t>
-        </is>
-      </c>
-      <c r="H357" t="inlineStr">
-        <is>
-          <t>14:00:45</t>
-        </is>
-      </c>
-      <c r="I357" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="J357" t="n">
-        <v>31</v>
-      </c>
-      <c r="K357" t="n">
-        <v>316</v>
-      </c>
-      <c r="R357" t="inlineStr">
-        <is>
-          <t>SALESSE Laurine</t>
-        </is>
-      </c>
-      <c r="U357" t="inlineStr">
-        <is>
-          <t>85387</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="B358" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>Cross</t>
-        </is>
-      </c>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>Time Trials</t>
-        </is>
-      </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>2020-11-08</t>
-        </is>
-      </c>
-      <c r="H358" t="inlineStr">
-        <is>
-          <t>14:01:30</t>
-        </is>
-      </c>
-      <c r="I358" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="J358" t="n">
-        <v>13</v>
-      </c>
-      <c r="K358" t="n">
-        <v>317</v>
-      </c>
-      <c r="R358" t="inlineStr">
-        <is>
-          <t>SRIBAR Ria</t>
-        </is>
-      </c>
-      <c r="U358" t="inlineStr">
-        <is>
-          <t>75645</t>
         </is>
       </c>
     </row>
